--- a/data/trans_dic/P19-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en los últimos 6 meses han ido al dentista</t>
+          <t>Población que en los últimos 6 meses han ido al dentista (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,5; 26,28</t>
+          <t>19,65; 25,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,16; 25,24</t>
+          <t>19,05; 25,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,11; 32,17</t>
+          <t>25,3; 32,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,2; 27,01</t>
+          <t>19,15; 26,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,94; 34,65</t>
+          <t>27,7; 34,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,07; 33,07</t>
+          <t>26,03; 33,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,77; 37,89</t>
+          <t>31,14; 38,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,6; 32,6</t>
+          <t>26,54; 32,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,58; 29,43</t>
+          <t>24,5; 29,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,67; 28,29</t>
+          <t>23,73; 28,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,04; 33,89</t>
+          <t>28,91; 33,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,69; 28,56</t>
+          <t>23,64; 28,73</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,28; 27,83</t>
+          <t>22,1; 28,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,88; 26,63</t>
+          <t>21,02; 26,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,33; 31,28</t>
+          <t>25,41; 31,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,58; 25,37</t>
+          <t>10,87; 25,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,47; 34,84</t>
+          <t>28,73; 34,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,37; 33,51</t>
+          <t>27,43; 33,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,5; 38,67</t>
+          <t>32,42; 38,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,21; 30,25</t>
+          <t>25,08; 30,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,03; 30,37</t>
+          <t>26,01; 30,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24,9; 29,05</t>
+          <t>25,09; 29,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,91; 34,29</t>
+          <t>29,85; 34,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,25; 26,69</t>
+          <t>15,68; 26,66</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,2; 30,92</t>
+          <t>24,04; 31,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,37; 30,18</t>
+          <t>23,06; 29,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,81; 35,05</t>
+          <t>27,61; 34,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,03; 36,29</t>
+          <t>27,95; 36,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,73; 36,08</t>
+          <t>29,21; 36,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,16; 32,84</t>
+          <t>25,85; 32,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,55; 38,14</t>
+          <t>31,28; 38,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,95; 39,4</t>
+          <t>14,76; 39,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,47; 32,47</t>
+          <t>27,47; 32,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,63; 30,35</t>
+          <t>25,42; 30,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,51; 35,43</t>
+          <t>30,76; 35,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,64; 35,84</t>
+          <t>20,66; 36,32</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,96; 27,34</t>
+          <t>21,94; 27,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,09; 29,01</t>
+          <t>23,26; 29,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,52; 32,02</t>
+          <t>25,5; 31,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,0; 32,48</t>
+          <t>25,83; 32,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,97; 34,0</t>
+          <t>27,78; 33,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,93; 34,76</t>
+          <t>29,01; 35,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,33; 36,05</t>
+          <t>29,69; 35,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,16; 36,24</t>
+          <t>26,31; 36,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,76; 29,73</t>
+          <t>25,83; 29,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,03; 31,11</t>
+          <t>27,04; 31,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,91; 33,15</t>
+          <t>28,98; 33,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,99; 33,47</t>
+          <t>27,46; 33,51</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,24; 26,34</t>
+          <t>23,38; 26,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,17; 26,08</t>
+          <t>23,24; 26,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27,33; 30,59</t>
+          <t>27,52; 30,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,92; 27,71</t>
+          <t>19,49; 27,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,8; 32,86</t>
+          <t>29,78; 33,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,85; 32,02</t>
+          <t>28,62; 31,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,89; 36,09</t>
+          <t>32,96; 36,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>24,2; 32,76</t>
+          <t>24,36; 32,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,03; 29,2</t>
+          <t>26,97; 29,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,49; 28,68</t>
+          <t>26,42; 28,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,55; 32,94</t>
+          <t>30,72; 33,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,28; 29,69</t>
+          <t>23,69; 29,62</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en los últimos 6 meses han ido al dentista</t>
+          <t>Población que en los últimos 6 meses han ido al dentista (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>135355; 182395</t>
+          <t>136386; 179141</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>134285; 176928</t>
+          <t>133552; 176324</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>169433; 217101</t>
+          <t>170751; 217257</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>121479; 170899</t>
+          <t>121179; 168443</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>192098; 238205</t>
+          <t>190383; 238359</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>181723; 230500</t>
+          <t>181462; 230697</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>207036; 254953</t>
+          <t>209527; 255873</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>178620; 218945</t>
+          <t>178203; 217869</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>339510; 406561</t>
+          <t>338421; 402328</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>330869; 395532</t>
+          <t>331792; 399479</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>391416; 456678</t>
+          <t>389663; 457278</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>308946; 372505</t>
+          <t>308369; 374740</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>214253; 267705</t>
+          <t>212528; 271050</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>212598; 271091</t>
+          <t>213975; 270496</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>258971; 319807</t>
+          <t>259754; 321164</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125554; 300925</t>
+          <t>128966; 301943</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>275711; 337371</t>
+          <t>278174; 335381</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>282464; 345862</t>
+          <t>283127; 343670</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>338930; 403250</t>
+          <t>338116; 405949</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>240642; 288716</t>
+          <t>239349; 289291</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>502517; 586132</t>
+          <t>501966; 583663</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510520; 595649</t>
+          <t>514335; 599599</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>617722; 708165</t>
+          <t>616432; 704721</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>326505; 571336</t>
+          <t>335620; 570800</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>164171; 209806</t>
+          <t>163129; 211194</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>177067; 228681</t>
+          <t>174683; 226394</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>211263; 266236</t>
+          <t>209729; 264067</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>197306; 255426</t>
+          <t>196684; 254540</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>196449; 246751</t>
+          <t>199749; 248273</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>203336; 255186</t>
+          <t>200895; 254349</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>247693; 299408</t>
+          <t>245577; 299651</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>138411; 364811</t>
+          <t>136661; 368118</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>374246; 442293</t>
+          <t>374201; 443114</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>393344; 465793</t>
+          <t>390148; 464557</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>471213; 547244</t>
+          <t>475053; 552450</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>320149; 584068</t>
+          <t>336680; 591882</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>206731; 257358</t>
+          <t>206496; 258784</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>218821; 274952</t>
+          <t>220419; 277651</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>239247; 300205</t>
+          <t>239095; 294736</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>237497; 296714</t>
+          <t>236010; 296309</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>290458; 353136</t>
+          <t>288558; 349888</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>304014; 365290</t>
+          <t>304863; 368761</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>316604; 376236</t>
+          <t>309936; 375599</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>281963; 390591</t>
+          <t>283610; 388081</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>509991; 588553</t>
+          <t>511381; 590955</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>540250; 621748</t>
+          <t>540460; 627770</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>572789; 656800</t>
+          <t>574242; 655447</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>537525; 666471</t>
+          <t>546922; 667310</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>761136; 862782</t>
+          <t>765770; 869320</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>793371; 893185</t>
+          <t>795892; 897514</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>927665; 1038411</t>
+          <t>934257; 1035721</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>650025; 952093</t>
+          <t>669893; 947806</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1006886; 1110122</t>
+          <t>1006060; 1115428</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1026159; 1139075</t>
+          <t>1018088; 1129440</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1165881; 1279347</t>
+          <t>1168344; 1281496</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>878391; 1189142</t>
+          <t>884215; 1187018</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1798612; 1942870</t>
+          <t>1794572; 1949930</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1849388; 2002245</t>
+          <t>1844792; 1998460</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2120052; 2285927</t>
+          <t>2131619; 2290065</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1715635; 2097718</t>
+          <t>1673995; 2093062</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,65; 25,81</t>
+          <t>19,72; 25,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,05; 25,15</t>
+          <t>18,94; 25,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,3; 32,2</t>
+          <t>25,14; 31,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,15; 26,62</t>
+          <t>18,4; 25,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,7; 34,67</t>
+          <t>27,33; 34,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,03; 33,1</t>
+          <t>25,98; 33,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,14; 38,03</t>
+          <t>30,91; 37,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,54; 32,44</t>
+          <t>26,01; 31,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,5; 29,12</t>
+          <t>24,59; 29,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,73; 28,57</t>
+          <t>23,39; 28,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,91; 33,93</t>
+          <t>28,97; 33,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,64; 28,73</t>
+          <t>23,39; 27,88</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,1; 28,18</t>
+          <t>22,12; 27,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,02; 26,57</t>
+          <t>21,04; 26,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,41; 31,41</t>
+          <t>25,1; 30,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,87; 25,45</t>
+          <t>20,81; 26,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,73; 34,63</t>
+          <t>28,44; 34,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,43; 33,3</t>
+          <t>27,33; 33,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,42; 38,92</t>
+          <t>32,61; 39,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,08; 30,31</t>
+          <t>24,77; 29,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,01; 30,24</t>
+          <t>26,13; 30,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,09; 29,25</t>
+          <t>24,87; 28,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,85; 34,12</t>
+          <t>30,03; 34,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,68; 26,66</t>
+          <t>23,68; 27,55</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,04; 31,13</t>
+          <t>24,03; 31,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,06; 29,88</t>
+          <t>23,37; 30,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,61; 34,77</t>
+          <t>27,82; 34,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,95; 36,17</t>
+          <t>26,35; 33,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,21; 36,31</t>
+          <t>29,14; 35,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,85; 32,73</t>
+          <t>25,72; 32,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,28; 38,17</t>
+          <t>31,99; 38,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,76; 39,75</t>
+          <t>30,71; 36,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,47; 32,53</t>
+          <t>27,7; 32,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,42; 30,27</t>
+          <t>25,57; 30,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,76; 35,77</t>
+          <t>30,71; 35,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,66; 36,32</t>
+          <t>29,45; 34,2</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,94; 27,49</t>
+          <t>21,81; 27,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,26; 29,3</t>
+          <t>23,08; 29,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,5; 31,44</t>
+          <t>25,87; 31,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,83; 32,43</t>
+          <t>26,01; 32,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,78; 33,69</t>
+          <t>27,63; 33,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,01; 35,09</t>
+          <t>29,22; 34,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,69; 35,98</t>
+          <t>30,29; 36,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,31; 36,01</t>
+          <t>31,97; 37,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,83; 29,85</t>
+          <t>25,82; 29,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,04; 31,41</t>
+          <t>26,99; 31,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,98; 33,08</t>
+          <t>28,93; 33,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,46; 33,51</t>
+          <t>30,05; 34,04</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,38; 26,54</t>
+          <t>23,42; 26,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,24; 26,21</t>
+          <t>23,19; 26,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27,52; 30,51</t>
+          <t>27,66; 30,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,49; 27,58</t>
+          <t>24,69; 27,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,78; 33,02</t>
+          <t>29,83; 33,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,62; 31,75</t>
+          <t>28,65; 31,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,96; 36,15</t>
+          <t>32,94; 36,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>24,36; 32,7</t>
+          <t>29,9; 32,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26,97; 29,31</t>
+          <t>27,15; 29,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,42; 28,62</t>
+          <t>26,45; 28,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,72; 33,0</t>
+          <t>30,69; 33,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,69; 29,62</t>
+          <t>27,74; 29,88</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>143302</t>
+          <t>152490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>197393</t>
+          <t>209704</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>340695</t>
+          <t>362194</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>136386; 179141</t>
+          <t>136825; 178516</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>133552; 176324</t>
+          <t>132786; 179147</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>170751; 217257</t>
+          <t>169652; 214735</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>121179; 168443</t>
+          <t>126516; 175314</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>190383; 238359</t>
+          <t>187906; 237271</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>181462; 230697</t>
+          <t>181114; 231558</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>209527; 255873</t>
+          <t>207958; 255467</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>178203; 217869</t>
+          <t>189589; 231211</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>338421; 402328</t>
+          <t>339673; 403447</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>331792; 399479</t>
+          <t>327030; 395668</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>389663; 457278</t>
+          <t>390421; 457918</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>308369; 374740</t>
+          <t>331346; 394973</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>229713</t>
+          <t>248542</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>263841</t>
+          <t>289686</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>493554</t>
+          <t>538227</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>212528; 271050</t>
+          <t>212791; 267282</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>213975; 270496</t>
+          <t>214192; 267027</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>259754; 321164</t>
+          <t>256581; 314504</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>128966; 301943</t>
+          <t>216748; 279819</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>278174; 335381</t>
+          <t>275452; 335151</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>283127; 343670</t>
+          <t>282129; 342202</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>338116; 405949</t>
+          <t>340138; 407512</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>239349; 289291</t>
+          <t>264295; 316715</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>501966; 583663</t>
+          <t>504295; 582598</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514335; 599599</t>
+          <t>509892; 592258</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>616432; 704721</t>
+          <t>620288; 706927</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>335620; 570800</t>
+          <t>499166; 580730</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>224665</t>
+          <t>240379</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>268809</t>
+          <t>270402</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>493474</t>
+          <t>510781</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>163129; 211194</t>
+          <t>163029; 211354</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>174683; 226394</t>
+          <t>177047; 228150</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>209729; 264067</t>
+          <t>211275; 262944</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>196684; 254540</t>
+          <t>211386; 271568</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>199749; 248273</t>
+          <t>199287; 245634</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>200895; 254349</t>
+          <t>199892; 252101</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>245577; 299651</t>
+          <t>251123; 302159</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>136661; 368118</t>
+          <t>246834; 295007</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>374201; 443114</t>
+          <t>377435; 443764</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>390148; 464557</t>
+          <t>392436; 467317</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>475053; 552450</t>
+          <t>474297; 548524</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>336680; 591882</t>
+          <t>472887; 549167</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>265032</t>
+          <t>281703</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>354190</t>
+          <t>382140</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>619223</t>
+          <t>663843</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>206496; 258784</t>
+          <t>205320; 260121</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>220419; 277651</t>
+          <t>218753; 275476</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>239095; 294736</t>
+          <t>242530; 298293</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>236010; 296309</t>
+          <t>253788; 314715</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>288558; 349888</t>
+          <t>286961; 346675</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>304863; 368761</t>
+          <t>307056; 365865</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>309936; 375599</t>
+          <t>316123; 376568</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>283610; 388081</t>
+          <t>351473; 407946</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>511381; 590955</t>
+          <t>511264; 590882</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>540460; 627770</t>
+          <t>539541; 626297</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>574242; 655447</t>
+          <t>573201; 657605</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>546922; 667310</t>
+          <t>623613; 706446</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>862713</t>
+          <t>923114</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1084234</t>
+          <t>1151931</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1946946</t>
+          <t>2075045</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>765770; 869320</t>
+          <t>767116; 869016</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>795892; 897514</t>
+          <t>793953; 900175</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>934257; 1035721</t>
+          <t>939015; 1038925</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>669893; 947806</t>
+          <t>865964; 978975</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1006060; 1115428</t>
+          <t>1007614; 1115681</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1018088; 1129440</t>
+          <t>1019104; 1132904</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1168344; 1281496</t>
+          <t>1167396; 1283111</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>884215; 1187018</t>
+          <t>1105992; 1205191</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1794572; 1949930</t>
+          <t>1806499; 1946168</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1844792; 1998460</t>
+          <t>1846546; 2001610</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2131619; 2290065</t>
+          <t>2129771; 2289983</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1673995; 2093062</t>
+          <t>1999274; 2152988</t>
         </is>
       </c>
     </row>
